--- a/tests/workbooktests/workbooks/test_shortratemodels.xlsx
+++ b/tests/workbooktests/workbooks/test_shortratemodels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41254BBE-A25D-4599-8D87-0B03E8218CB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C249AA64-1E29-4B6F-ACF1-C055482E16A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3885" yWindow="-18240" windowWidth="30690" windowHeight="16530" xr2:uid="{A576409D-E527-4FE8-BADF-F8DE357B9837}"/>
   </bookViews>
@@ -481,6 +481,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -498,22 +514,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,22 +839,22 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="25"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="22"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="12" t="s">
         <v>7</v>
       </c>
@@ -890,10 +890,10 @@
       <c r="D4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G4" s="9"/>
@@ -911,18 +911,18 @@
       <c r="D5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="J5" s="22" t="s">
         <v>55</v>
       </c>
     </row>
@@ -953,10 +953,10 @@
       <c r="D7" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G7" s="9"/>
@@ -968,22 +968,22 @@
       <c r="B8" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="25"/>
+      <c r="D8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31" t="s">
+      <c r="E8" s="25"/>
+      <c r="F8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="32"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1239,7 +1239,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R22C3YieldTermStructureHandle,A</v>
       </c>
       <c r="D22" s="8"/>
@@ -1276,7 +1276,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R25C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B27" s="8">
@@ -1305,7 +1305,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8">
         <v>0.5</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="C29" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R29C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>31</v>
       </c>
       <c r="C31" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R31C3YieldTermStructureHandle,A</v>
       </c>
       <c r="D31" s="8"/>
@@ -1377,7 +1377,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B36" s="8">
@@ -1406,7 +1406,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="8">
         <v>0.5</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]Vasicek!R38C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1473,11 +1473,11 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C4" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R4C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R27C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>31</v>
       </c>
       <c r="C30" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R30C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="8">
@@ -1799,7 +1799,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="26"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="8">
         <v>0.5</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R34C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R36C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R39C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B41" s="8">
@@ -1896,7 +1896,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="26"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="8">
         <v>0.5</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R43C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       <c r="A48" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="23">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
@@ -2007,11 +2007,11 @@
         <v>72</v>
       </c>
       <c r="B53" s="8" t="str">
-        <f>_xll.qlFlatForward($B$1,0)</f>
+        <f>_xll.qlFlatForward($B$1,0,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R53C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C53" s="8" t="str">
-        <f>_xll.qlFlatForward($B$1,0)</f>
+        <f>_xll.qlFlatForward($B$1,0,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R53C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2020,11 +2020,11 @@
         <v>73</v>
       </c>
       <c r="B54" s="8" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R54C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C54" s="8" t="str">
-        <f>_xll.qlFlatForward($B$1,0.02)</f>
+        <f>_xll.qlFlatForward($B$1,0.02,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]HullWhite!R54C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="24" t="s">
         <v>70</v>
       </c>
       <c r="B56" s="8" t="str">
@@ -2104,11 +2104,11 @@
         <v>31</v>
       </c>
       <c r="B4" s="19" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C4" s="19" t="str">
-        <f>_xll.qlFlatForward(C$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R4C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R10C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="8">
@@ -2199,7 +2199,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="8">
         <v>0.5</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R14C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R17C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B19" s="8">
@@ -2274,7 +2274,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="8">
         <v>0.5</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]BlackKarasinski!R21C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R21C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>31</v>
       </c>
       <c r="C24" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R24C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="8">
@@ -2589,7 +2589,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="8">
         <v>0.5</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R28C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <v>31</v>
       </c>
       <c r="C30" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R30C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R33C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="8">
@@ -2686,7 +2686,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="8">
         <v>0.5</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>31</v>
       </c>
       <c r="C37" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R37C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2724,11 +2724,11 @@
         <v>31</v>
       </c>
       <c r="B41" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(A$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R41C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C41" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R41C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R60C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
         <v>31</v>
       </c>
       <c r="C63" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R63C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" t="s">
+      <c r="A65" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B65" s="8">
@@ -2997,7 +2997,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="26"/>
+      <c r="A66" s="32"/>
       <c r="B66" s="8">
         <v>0.5</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>31</v>
       </c>
       <c r="C67" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R67C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
         <v>31</v>
       </c>
       <c r="C69" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R69C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
         <v>31</v>
       </c>
       <c r="C72" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R72C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="26" t="s">
+      <c r="A74" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B74" s="8">
@@ -3094,7 +3094,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="26"/>
+      <c r="A75" s="32"/>
       <c r="B75" s="8">
         <v>0.5</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>31</v>
       </c>
       <c r="C76" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]CoxIngersollRoss!R76C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(B$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C4" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R4C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="32" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="8">
@@ -3282,7 +3282,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="8">
         <v>0</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R25C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B27" s="8">
@@ -3418,7 +3418,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="8">
         <v>0.5</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>31</v>
       </c>
       <c r="C29" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R29C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R32C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="32" t="s">
         <v>58</v>
       </c>
       <c r="B34" s="8">
@@ -3493,7 +3493,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="8">
         <v>0.5</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="8" t="str">
-        <f>_xll.qlFlatForward(B$1,0.04)</f>
+        <f>_xll.qlFlatForward(C$1,0.04,"actual365fixed")</f>
         <v>欣[test_shortratemodels.xlsx]G2Model!R36C3YieldTermStructureHandle,A</v>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       <c r="A45" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="23">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
